--- a/annotation/annotation_ibrahim.xlsx
+++ b/annotation/annotation_ibrahim.xlsx
@@ -600,7 +600,11 @@
           <t>arigato</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n"/>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -616,7 +620,11 @@
           <t>counselor'ı</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -632,7 +640,11 @@
           <t>real,</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -648,7 +660,11 @@
           <t>hey</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -664,7 +680,11 @@
           <t>aday</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -680,7 +700,11 @@
           <t>hackernewsta</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -696,7 +720,11 @@
           <t>pardon</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -712,7 +740,11 @@
           <t>bi</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -728,7 +760,11 @@
           <t>bitte</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -744,7 +780,11 @@
           <t>spotify'a</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -760,7 +800,11 @@
           <t>skill'leri</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -776,7 +820,11 @@
           <t>youtube</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -792,7 +840,11 @@
           <t>linkedin</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -808,7 +860,11 @@
           <t>what</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -824,7 +880,11 @@
           <t>ooh</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -840,7 +900,11 @@
           <t>anime</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -856,7 +920,11 @@
           <t>büyüdü,</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -872,7 +940,11 @@
           <t>büyük</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -888,7 +960,11 @@
           <t>erasmus</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -904,7 +980,11 @@
           <t>"x</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -920,7 +1000,11 @@
           <t>reels'lerin</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -936,7 +1020,11 @@
           <t>kendime</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n"/>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -952,7 +1040,11 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D24" s="5" t="n"/>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -968,7 +1060,11 @@
           <t>formuna</t>
         </is>
       </c>
-      <c r="D25" s="5" t="n"/>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -984,7 +1080,11 @@
           <t>türk</t>
         </is>
       </c>
-      <c r="D26" s="5" t="n"/>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1000,7 +1100,11 @@
           <t>swiftuı</t>
         </is>
       </c>
-      <c r="D27" s="5" t="n"/>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1016,7 +1120,11 @@
           <t>batman</t>
         </is>
       </c>
-      <c r="D28" s="5" t="n"/>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1032,7 +1140,11 @@
           <t>williams'ın</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n"/>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1048,7 +1160,11 @@
           <t>duyurmuş.**</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n"/>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1064,7 +1180,11 @@
           <t>networking</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n"/>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1080,7 +1200,11 @@
           <t>gaming</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n"/>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1096,7 +1220,11 @@
           <t>walt</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n"/>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1112,7 +1240,11 @@
           <t>cripte-sceptic</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n"/>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1128,7 +1260,11 @@
           <t>printten</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n"/>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1144,7 +1280,11 @@
           <t>out</t>
         </is>
       </c>
-      <c r="D36" s="5" t="n"/>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1160,7 +1300,11 @@
           <t>discord</t>
         </is>
       </c>
-      <c r="D37" s="5" t="n"/>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1176,7 +1320,11 @@
           <t>bakınca</t>
         </is>
       </c>
-      <c r="D38" s="5" t="n"/>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1192,7 +1340,11 @@
           <t>araci</t>
         </is>
       </c>
-      <c r="D39" s="5" t="n"/>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1208,7 +1360,11 @@
           <t>chant'leri</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n"/>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1224,7 +1380,11 @@
           <t>sonra</t>
         </is>
       </c>
-      <c r="D41" s="5" t="n"/>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1240,7 +1400,11 @@
           <t>track'ler</t>
         </is>
       </c>
-      <c r="D42" s="5" t="n"/>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1256,7 +1420,11 @@
           <t>flac</t>
         </is>
       </c>
-      <c r="D43" s="5" t="n"/>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1272,7 +1440,11 @@
           <t>editleyip</t>
         </is>
       </c>
-      <c r="D44" s="5" t="n"/>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1288,7 +1460,11 @@
           <t>icin</t>
         </is>
       </c>
-      <c r="D45" s="5" t="n"/>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1304,7 +1480,11 @@
           <t>lol'sun</t>
         </is>
       </c>
-      <c r="D46" s="5" t="n"/>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1320,7 +1500,11 @@
           <t>spotify</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n"/>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1336,7 +1520,11 @@
           <t>setup'ı</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n"/>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1352,7 +1540,11 @@
           <t>final</t>
         </is>
       </c>
-      <c r="D49" s="5" t="n"/>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1368,7 +1560,11 @@
           <t>session'ı</t>
         </is>
       </c>
-      <c r="D50" s="5" t="n"/>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1384,7 +1580,11 @@
           <t>seinen</t>
         </is>
       </c>
-      <c r="D51" s="5" t="n"/>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1400,7 +1600,11 @@
           <t>de</t>
         </is>
       </c>
-      <c r="D52" s="5" t="n"/>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1416,7 +1620,11 @@
           <t>talk</t>
         </is>
       </c>
-      <c r="D53" s="5" t="n"/>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1432,7 +1640,11 @@
           <t>subreddit'lerinde</t>
         </is>
       </c>
-      <c r="D54" s="5" t="n"/>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1448,7 +1660,11 @@
           <t>duolingo'nun</t>
         </is>
       </c>
-      <c r="D55" s="5" t="n"/>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1464,7 +1680,11 @@
           <t>hizli,</t>
         </is>
       </c>
-      <c r="D56" s="5" t="n"/>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1480,7 +1700,11 @@
           <t>round'da</t>
         </is>
       </c>
-      <c r="D57" s="5" t="n"/>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1496,7 +1720,11 @@
           <t>satıştan</t>
         </is>
       </c>
-      <c r="D58" s="5" t="n"/>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1512,7 +1740,11 @@
           <t>amerika</t>
         </is>
       </c>
-      <c r="D59" s="5" t="n"/>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1528,7 +1760,11 @@
           <t>olarak</t>
         </is>
       </c>
-      <c r="D60" s="5" t="n"/>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1544,7 +1780,11 @@
           <t>instagram'a</t>
         </is>
       </c>
-      <c r="D61" s="5" t="n"/>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1560,7 +1800,11 @@
           <t>potter'i</t>
         </is>
       </c>
-      <c r="D62" s="5" t="n"/>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1576,7 +1820,11 @@
           <t>broth'u</t>
         </is>
       </c>
-      <c r="D63" s="5" t="n"/>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1592,7 +1840,11 @@
           <t>mangasından</t>
         </is>
       </c>
-      <c r="D64" s="5" t="n"/>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1608,7 +1860,11 @@
           <t>seklinde</t>
         </is>
       </c>
-      <c r="D65" s="5" t="n"/>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1624,7 +1880,11 @@
           <t>saçmalığa</t>
         </is>
       </c>
-      <c r="D66" s="5" t="n"/>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1640,7 +1900,11 @@
           <t>her</t>
         </is>
       </c>
-      <c r="D67" s="5" t="n"/>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1656,7 +1920,11 @@
           <t>manager'ım</t>
         </is>
       </c>
-      <c r="D68" s="5" t="n"/>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1672,7 +1940,11 @@
           <t>patternleri</t>
         </is>
       </c>
-      <c r="D69" s="5" t="n"/>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1688,7 +1960,11 @@
           <t>grooveshark</t>
         </is>
       </c>
-      <c r="D70" s="5" t="n"/>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1704,7 +1980,11 @@
           <t>kodumu</t>
         </is>
       </c>
-      <c r="D71" s="5" t="n"/>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1720,7 +2000,11 @@
           <t>tv'leri</t>
         </is>
       </c>
-      <c r="D72" s="5" t="n"/>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1736,7 +2020,11 @@
           <t>searche</t>
         </is>
       </c>
-      <c r="D73" s="5" t="n"/>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1752,7 +2040,11 @@
           <t>everything'i</t>
         </is>
       </c>
-      <c r="D74" s="5" t="n"/>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1768,7 +2060,11 @@
           <t>daily</t>
         </is>
       </c>
-      <c r="D75" s="5" t="n"/>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1784,7 +2080,11 @@
           <t>anasayfanızda</t>
         </is>
       </c>
-      <c r="D76" s="5" t="n"/>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1800,7 +2100,11 @@
           <t>ajet</t>
         </is>
       </c>
-      <c r="D77" s="5" t="n"/>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1816,7 +2120,11 @@
           <t>listede</t>
         </is>
       </c>
-      <c r="D78" s="5" t="n"/>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1832,7 +2140,11 @@
           <t>boys</t>
         </is>
       </c>
-      <c r="D79" s="5" t="n"/>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1848,7 +2160,11 @@
           <t>facebook,</t>
         </is>
       </c>
-      <c r="D80" s="5" t="n"/>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1864,7 +2180,11 @@
           <t>"askreddit"</t>
         </is>
       </c>
-      <c r="D81" s="5" t="n"/>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1880,7 +2200,11 @@
           <t>ligi</t>
         </is>
       </c>
-      <c r="D82" s="5" t="n"/>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1896,7 +2220,11 @@
           <t>fırat</t>
         </is>
       </c>
-      <c r="D83" s="5" t="n"/>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1912,7 +2240,11 @@
           <t>anime</t>
         </is>
       </c>
-      <c r="D84" s="5" t="n"/>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1928,7 +2260,11 @@
           <t>sistemi</t>
         </is>
       </c>
-      <c r="D85" s="5" t="n"/>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1944,7 +2280,11 @@
           <t>intranet'inde</t>
         </is>
       </c>
-      <c r="D86" s="5" t="n"/>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1960,7 +2300,11 @@
           <t>link</t>
         </is>
       </c>
-      <c r="D87" s="5" t="n"/>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1976,7 +2320,11 @@
           <t>photography</t>
         </is>
       </c>
-      <c r="D88" s="5" t="n"/>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1992,7 +2340,11 @@
           <t>hygge</t>
         </is>
       </c>
-      <c r="D89" s="5" t="n"/>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2008,7 +2360,11 @@
           <t>for</t>
         </is>
       </c>
-      <c r="D90" s="5" t="n"/>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2024,7 +2380,11 @@
           <t>zodiac</t>
         </is>
       </c>
-      <c r="D91" s="5" t="n"/>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2040,7 +2400,11 @@
           <t>assumption</t>
         </is>
       </c>
-      <c r="D92" s="5" t="n"/>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2056,7 +2420,11 @@
           <t>quiz'leri</t>
         </is>
       </c>
-      <c r="D93" s="5" t="n"/>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2072,7 +2440,11 @@
           <t>twitter'da</t>
         </is>
       </c>
-      <c r="D94" s="5" t="n"/>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2088,7 +2460,11 @@
           <t>at</t>
         </is>
       </c>
-      <c r="D95" s="5" t="n"/>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2104,7 +2480,11 @@
           <t>kalmis</t>
         </is>
       </c>
-      <c r="D96" s="5" t="n"/>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2120,7 +2500,11 @@
           <t>festivali'nde</t>
         </is>
       </c>
-      <c r="D97" s="5" t="n"/>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2136,7 +2520,11 @@
           <t>ankara'dan</t>
         </is>
       </c>
-      <c r="D98" s="5" t="n"/>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2152,7 +2540,11 @@
           <t>zoomies</t>
         </is>
       </c>
-      <c r="D99" s="5" t="n"/>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2168,7 +2560,11 @@
           <t>overcapacity'si</t>
         </is>
       </c>
-      <c r="D100" s="5" t="n"/>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2184,7 +2580,11 @@
           <t>banka</t>
         </is>
       </c>
-      <c r="D101" s="5" t="n"/>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2200,7 +2600,11 @@
           <t>dark</t>
         </is>
       </c>
-      <c r="D102" s="5" t="n"/>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2216,7 +2620,11 @@
           <t>twitter'ında</t>
         </is>
       </c>
-      <c r="D103" s="5" t="n"/>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2232,7 +2640,11 @@
           <t>arama</t>
         </is>
       </c>
-      <c r="D104" s="5" t="n"/>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2248,7 +2660,11 @@
           <t>arkadan</t>
         </is>
       </c>
-      <c r="D105" s="5" t="n"/>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2264,7 +2680,11 @@
           <t>impostorlar</t>
         </is>
       </c>
-      <c r="D106" s="5" t="n"/>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2280,7 +2700,11 @@
           <t>haklarinda</t>
         </is>
       </c>
-      <c r="D107" s="5" t="n"/>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2296,7 +2720,11 @@
           <t>reason</t>
         </is>
       </c>
-      <c r="D108" s="5" t="n"/>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2312,7 +2740,11 @@
           <t>protein</t>
         </is>
       </c>
-      <c r="D109" s="5" t="n"/>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2328,7 +2760,11 @@
           <t>her</t>
         </is>
       </c>
-      <c r="D110" s="5" t="n"/>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2344,7 +2780,11 @@
           <t>limitiniz</t>
         </is>
       </c>
-      <c r="D111" s="5" t="n"/>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2360,7 +2800,11 @@
           <t>reposunu</t>
         </is>
       </c>
-      <c r="D112" s="5" t="n"/>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2376,7 +2820,11 @@
           <t>lab</t>
         </is>
       </c>
-      <c r="D113" s="5" t="n"/>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2392,7 +2840,11 @@
           <t>iphone</t>
         </is>
       </c>
-      <c r="D114" s="5" t="n"/>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2408,7 +2860,11 @@
           <t>parka</t>
         </is>
       </c>
-      <c r="D115" s="5" t="n"/>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2424,7 +2880,11 @@
           <t>çevreci</t>
         </is>
       </c>
-      <c r="D116" s="5" t="n"/>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2440,7 +2900,11 @@
           <t>swipe'lamaktan</t>
         </is>
       </c>
-      <c r="D117" s="5" t="n"/>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2456,7 +2920,11 @@
           <t>youtuber'ların</t>
         </is>
       </c>
-      <c r="D118" s="5" t="n"/>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2472,7 +2940,11 @@
           <t>meeting'e</t>
         </is>
       </c>
-      <c r="D119" s="5" t="n"/>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2488,7 +2960,11 @@
           <t>murat</t>
         </is>
       </c>
-      <c r="D120" s="5" t="n"/>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2504,7 +2980,11 @@
           <t>alınca</t>
         </is>
       </c>
-      <c r="D121" s="5" t="n"/>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2520,7 +3000,11 @@
           <t>yapılıyor</t>
         </is>
       </c>
-      <c r="D122" s="5" t="n"/>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2536,7 +3020,11 @@
           <t>vitamin</t>
         </is>
       </c>
-      <c r="D123" s="5" t="n"/>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2552,7 +3040,11 @@
           <t>çıplak</t>
         </is>
       </c>
-      <c r="D124" s="5" t="n"/>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2568,7 +3060,11 @@
           <t>years</t>
         </is>
       </c>
-      <c r="D125" s="5" t="n"/>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2584,7 +3080,11 @@
           <t>garden</t>
         </is>
       </c>
-      <c r="D126" s="5" t="n"/>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2600,7 +3100,11 @@
           <t>meksika'dan</t>
         </is>
       </c>
-      <c r="D127" s="5" t="n"/>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2616,7 +3120,11 @@
           <t>doğalgaz</t>
         </is>
       </c>
-      <c r="D128" s="5" t="n"/>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -2632,7 +3140,11 @@
           <t>study</t>
         </is>
       </c>
-      <c r="D129" s="5" t="n"/>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -2648,7 +3160,11 @@
           <t>varsayımından</t>
         </is>
       </c>
-      <c r="D130" s="5" t="n"/>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -2664,7 +3180,11 @@
           <t>youtube'dan</t>
         </is>
       </c>
-      <c r="D131" s="5" t="n"/>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -2680,7 +3200,11 @@
           <t>self</t>
         </is>
       </c>
-      <c r="D132" s="5" t="n"/>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -2696,7 +3220,11 @@
           <t>lego</t>
         </is>
       </c>
-      <c r="D133" s="5" t="n"/>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -2712,7 +3240,11 @@
           <t>multivitamin</t>
         </is>
       </c>
-      <c r="D134" s="5" t="n"/>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -2728,7 +3260,11 @@
           <t>olması</t>
         </is>
       </c>
-      <c r="D135" s="5" t="n"/>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -2744,7 +3280,11 @@
           <t>home</t>
         </is>
       </c>
-      <c r="D136" s="5" t="n"/>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -2760,7 +3300,11 @@
           <t>results</t>
         </is>
       </c>
-      <c r="D137" s="5" t="n"/>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -2776,7 +3320,11 @@
           <t>remix'leri</t>
         </is>
       </c>
-      <c r="D138" s="5" t="n"/>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2792,7 +3340,11 @@
           <t>de</t>
         </is>
       </c>
-      <c r="D139" s="5" t="n"/>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -2808,7 +3360,11 @@
           <t>allasen</t>
         </is>
       </c>
-      <c r="D140" s="5" t="n"/>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -2824,7 +3380,11 @@
           <t>platform</t>
         </is>
       </c>
-      <c r="D141" s="5" t="n"/>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -2840,7 +3400,11 @@
           <t>of</t>
         </is>
       </c>
-      <c r="D142" s="5" t="n"/>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -2856,7 +3420,11 @@
           <t>uykusuz</t>
         </is>
       </c>
-      <c r="D143" s="5" t="n"/>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2872,7 +3440,11 @@
           <t>arkadaşım</t>
         </is>
       </c>
-      <c r="D144" s="5" t="n"/>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -2888,7 +3460,11 @@
           <t>için</t>
         </is>
       </c>
-      <c r="D145" s="5" t="n"/>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -2904,7 +3480,11 @@
           <t>adana'da</t>
         </is>
       </c>
-      <c r="D146" s="5" t="n"/>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -2920,7 +3500,11 @@
           <t>vamos</t>
         </is>
       </c>
-      <c r="D147" s="5" t="n"/>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2936,7 +3520,11 @@
           <t>scenes</t>
         </is>
       </c>
-      <c r="D148" s="5" t="n"/>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2952,7 +3540,11 @@
           <t>fatpeoplehate</t>
         </is>
       </c>
-      <c r="D149" s="5" t="n"/>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -2968,7 +3560,11 @@
           <t>hookslar</t>
         </is>
       </c>
-      <c r="D150" s="5" t="n"/>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -2984,7 +3580,11 @@
           <t>imagine</t>
         </is>
       </c>
-      <c r="D151" s="5" t="n"/>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -3000,7 +3600,11 @@
           <t>papaganim</t>
         </is>
       </c>
-      <c r="D152" s="5" t="n"/>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -3016,7 +3620,11 @@
           <t>platform</t>
         </is>
       </c>
-      <c r="D153" s="5" t="n"/>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -3032,7 +3640,11 @@
           <t>trendle</t>
         </is>
       </c>
-      <c r="D154" s="5" t="n"/>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -3048,7 +3660,11 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="D155" s="5" t="n"/>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -3064,7 +3680,11 @@
           <t>feedback</t>
         </is>
       </c>
-      <c r="D156" s="5" t="n"/>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -3080,7 +3700,11 @@
           <t>kızın</t>
         </is>
       </c>
-      <c r="D157" s="5" t="n"/>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -3096,7 +3720,11 @@
           <t>demo'ları</t>
         </is>
       </c>
-      <c r="D158" s="5" t="n"/>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -3112,7 +3740,11 @@
           <t>next</t>
         </is>
       </c>
-      <c r="D159" s="5" t="n"/>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -3128,7 +3760,11 @@
           <t>anything</t>
         </is>
       </c>
-      <c r="D160" s="5" t="n"/>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -3144,7 +3780,11 @@
           <t>good</t>
         </is>
       </c>
-      <c r="D161" s="5" t="n"/>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -3160,7 +3800,11 @@
           <t>good,</t>
         </is>
       </c>
-      <c r="D162" s="5" t="n"/>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -3176,7 +3820,11 @@
           <t>platform</t>
         </is>
       </c>
-      <c r="D163" s="5" t="n"/>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -3192,7 +3840,11 @@
           <t>in</t>
         </is>
       </c>
-      <c r="D164" s="5" t="n"/>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -3208,7 +3860,11 @@
           <t>gelip</t>
         </is>
       </c>
-      <c r="D165" s="5" t="n"/>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -3224,7 +3880,11 @@
           <t>buildingten</t>
         </is>
       </c>
-      <c r="D166" s="5" t="n"/>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -3240,7 +3900,11 @@
           <t>izliyorsun,</t>
         </is>
       </c>
-      <c r="D167" s="5" t="n"/>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -3256,7 +3920,11 @@
           <t>bug'i</t>
         </is>
       </c>
-      <c r="D168" s="5" t="n"/>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -3272,7 +3940,11 @@
           <t>aldığım</t>
         </is>
       </c>
-      <c r="D169" s="5" t="n"/>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -3288,7 +3960,11 @@
           <t>bir</t>
         </is>
       </c>
-      <c r="D170" s="5" t="n"/>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -3304,7 +3980,11 @@
           <t>plugin</t>
         </is>
       </c>
-      <c r="D171" s="5" t="n"/>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -3320,7 +4000,11 @@
           <t>feed'lere</t>
         </is>
       </c>
-      <c r="D172" s="5" t="n"/>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -3336,7 +4020,11 @@
           <t>devamlı</t>
         </is>
       </c>
-      <c r="D173" s="5" t="n"/>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -3352,7 +4040,11 @@
           <t>headhunter'lar</t>
         </is>
       </c>
-      <c r="D174" s="5" t="n"/>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -3368,7 +4060,11 @@
           <t>twitter</t>
         </is>
       </c>
-      <c r="D175" s="5" t="n"/>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -3384,7 +4080,11 @@
           <t>android</t>
         </is>
       </c>
-      <c r="D176" s="5" t="n"/>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -3400,7 +4100,11 @@
           <t>model</t>
         </is>
       </c>
-      <c r="D177" s="5" t="n"/>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -3416,7 +4120,11 @@
           <t>ayda</t>
         </is>
       </c>
-      <c r="D178" s="5" t="n"/>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -3432,7 +4140,11 @@
           <t>could</t>
         </is>
       </c>
-      <c r="D179" s="5" t="n"/>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -3448,7 +4160,11 @@
           <t>simdi</t>
         </is>
       </c>
-      <c r="D180" s="5" t="n"/>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -3464,7 +4180,11 @@
           <t>şarkılar</t>
         </is>
       </c>
-      <c r="D181" s="5" t="n"/>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -3480,7 +4200,11 @@
           <t>şili</t>
         </is>
       </c>
-      <c r="D182" s="5" t="n"/>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -3496,7 +4220,11 @@
           <t>together"</t>
         </is>
       </c>
-      <c r="D183" s="5" t="n"/>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -3512,7 +4240,11 @@
           <t>herkes</t>
         </is>
       </c>
-      <c r="D184" s="5" t="n"/>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -3528,7 +4260,11 @@
           <t>zil</t>
         </is>
       </c>
-      <c r="D185" s="5" t="n"/>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -3544,7 +4280,11 @@
           <t>playstation</t>
         </is>
       </c>
-      <c r="D186" s="5" t="n"/>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -3560,7 +4300,11 @@
           <t>site</t>
         </is>
       </c>
-      <c r="D187" s="5" t="n"/>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -3576,7 +4320,11 @@
           <t>platform</t>
         </is>
       </c>
-      <c r="D188" s="5" t="n"/>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -3592,7 +4340,11 @@
           <t>düşünce</t>
         </is>
       </c>
-      <c r="D189" s="5" t="n"/>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -3608,7 +4360,11 @@
           <t>scaries</t>
         </is>
       </c>
-      <c r="D190" s="5" t="n"/>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -3624,7 +4380,11 @@
           <t>time</t>
         </is>
       </c>
-      <c r="D191" s="5" t="n"/>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -3640,7 +4400,11 @@
           <t>gibi</t>
         </is>
       </c>
-      <c r="D192" s="5" t="n"/>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -3656,7 +4420,11 @@
           <t>train'e</t>
         </is>
       </c>
-      <c r="D193" s="5" t="n"/>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -3672,7 +4440,11 @@
           <t>story'mde</t>
         </is>
       </c>
-      <c r="D194" s="5" t="n"/>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -3688,7 +4460,11 @@
           <t>o</t>
         </is>
       </c>
-      <c r="D195" s="5" t="n"/>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -3704,7 +4480,11 @@
           <t>son</t>
         </is>
       </c>
-      <c r="D196" s="5" t="n"/>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -3720,7 +4500,11 @@
           <t>route'ını</t>
         </is>
       </c>
-      <c r="D197" s="5" t="n"/>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -3736,7 +4520,11 @@
           <t>james</t>
         </is>
       </c>
-      <c r="D198" s="5" t="n"/>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -3752,7 +4540,11 @@
           <t>offline</t>
         </is>
       </c>
-      <c r="D199" s="5" t="n"/>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -3768,7 +4560,11 @@
           <t>passwordü</t>
         </is>
       </c>
-      <c r="D200" s="5" t="n"/>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -3784,7 +4580,11 @@
           <t>vb</t>
         </is>
       </c>
-      <c r="D201" s="5" t="n"/>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -3800,7 +4600,11 @@
           <t>bulacagiz</t>
         </is>
       </c>
-      <c r="D202" s="5" t="n"/>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -3816,7 +4620,11 @@
           <t>and</t>
         </is>
       </c>
-      <c r="D203" s="5" t="n"/>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -3832,7 +4640,11 @@
           <t>reaction'i</t>
         </is>
       </c>
-      <c r="D204" s="5" t="n"/>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -3848,7 +4660,11 @@
           <t>tv</t>
         </is>
       </c>
-      <c r="D205" s="5" t="n"/>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -3864,7 +4680,11 @@
           <t>kaç</t>
         </is>
       </c>
-      <c r="D206" s="5" t="n"/>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -3880,7 +4700,11 @@
           <t>vergilendirme</t>
         </is>
       </c>
-      <c r="D207" s="5" t="n"/>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -3896,7 +4720,11 @@
           <t>veganlar</t>
         </is>
       </c>
-      <c r="D208" s="5" t="n"/>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -3912,7 +4740,11 @@
           <t>sonra</t>
         </is>
       </c>
-      <c r="D209" s="5" t="n"/>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -3928,7 +4760,11 @@
           <t>google</t>
         </is>
       </c>
-      <c r="D210" s="5" t="n"/>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -3944,7 +4780,11 @@
           <t>policy'si</t>
         </is>
       </c>
-      <c r="D211" s="5" t="n"/>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -3960,7 +4800,11 @@
           <t>queue</t>
         </is>
       </c>
-      <c r="D212" s="5" t="n"/>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -3976,7 +4820,11 @@
           <t>birebir</t>
         </is>
       </c>
-      <c r="D213" s="5" t="n"/>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -3992,7 +4840,11 @@
           <t>yeaaa"</t>
         </is>
       </c>
-      <c r="D214" s="5" t="n"/>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -4008,7 +4860,11 @@
           <t>3d,</t>
         </is>
       </c>
-      <c r="D215" s="5" t="n"/>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -4024,7 +4880,11 @@
           <t>resmen</t>
         </is>
       </c>
-      <c r="D216" s="5" t="n"/>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -4040,7 +4900,11 @@
           <t>burger'ı</t>
         </is>
       </c>
-      <c r="D217" s="5" t="n"/>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -4056,7 +4920,11 @@
           <t>bir</t>
         </is>
       </c>
-      <c r="D218" s="5" t="n"/>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -4072,7 +4940,11 @@
           <t>thinking</t>
         </is>
       </c>
-      <c r="D219" s="5" t="n"/>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -4088,7 +4960,11 @@
           <t>chill"</t>
         </is>
       </c>
-      <c r="D220" s="5" t="n"/>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -4104,7 +4980,11 @@
           <t>toollar</t>
         </is>
       </c>
-      <c r="D221" s="5" t="n"/>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -4120,7 +5000,11 @@
           <t>örgü</t>
         </is>
       </c>
-      <c r="D222" s="5" t="n"/>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -4136,7 +5020,11 @@
           <t>ha,</t>
         </is>
       </c>
-      <c r="D223" s="5" t="n"/>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -4152,7 +5040,11 @@
           <t>delay'li</t>
         </is>
       </c>
-      <c r="D224" s="5" t="n"/>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -4168,7 +5060,11 @@
           <t>facebook,</t>
         </is>
       </c>
-      <c r="D225" s="5" t="n"/>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -4184,7 +5080,11 @@
           <t>filler</t>
         </is>
       </c>
-      <c r="D226" s="5" t="n"/>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -4200,7 +5100,11 @@
           <t>büyüledi,</t>
         </is>
       </c>
-      <c r="D227" s="5" t="n"/>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -4216,7 +5120,11 @@
           <t>üç</t>
         </is>
       </c>
-      <c r="D228" s="5" t="n"/>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -4232,7 +5140,11 @@
           <t>de</t>
         </is>
       </c>
-      <c r="D229" s="5" t="n"/>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -4248,7 +5160,11 @@
           <t>parks</t>
         </is>
       </c>
-      <c r="D230" s="5" t="n"/>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -4264,7 +5180,11 @@
           <t>edit</t>
         </is>
       </c>
-      <c r="D231" s="5" t="n"/>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -4280,7 +5200,11 @@
           <t>kendimize</t>
         </is>
       </c>
-      <c r="D232" s="5" t="n"/>
+      <c r="D232" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -4296,7 +5220,11 @@
           <t>kalır</t>
         </is>
       </c>
-      <c r="D233" s="5" t="n"/>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -4312,7 +5240,11 @@
           <t>youtube'ta</t>
         </is>
       </c>
-      <c r="D234" s="5" t="n"/>
+      <c r="D234" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -4328,7 +5260,11 @@
           <t>manga</t>
         </is>
       </c>
-      <c r="D235" s="5" t="n"/>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -4344,7 +5280,11 @@
           <t>angel'i</t>
         </is>
       </c>
-      <c r="D236" s="5" t="n"/>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -4360,7 +5300,11 @@
           <t>piano</t>
         </is>
       </c>
-      <c r="D237" s="5" t="n"/>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -4376,7 +5320,11 @@
           <t>generator</t>
         </is>
       </c>
-      <c r="D238" s="5" t="n"/>
+      <c r="D238" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -4392,7 +5340,11 @@
           <t>da</t>
         </is>
       </c>
-      <c r="D239" s="5" t="n"/>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -4408,7 +5360,11 @@
           <t>anime</t>
         </is>
       </c>
-      <c r="D240" s="5" t="n"/>
+      <c r="D240" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -4424,7 +5380,11 @@
           <t>çift</t>
         </is>
       </c>
-      <c r="D241" s="5" t="n"/>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -4440,7 +5400,11 @@
           <t>kendilerine</t>
         </is>
       </c>
-      <c r="D242" s="5" t="n"/>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -4456,7 +5420,11 @@
           <t>site</t>
         </is>
       </c>
-      <c r="D243" s="5" t="n"/>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -4472,7 +5440,11 @@
           <t>blister'lar</t>
         </is>
       </c>
-      <c r="D244" s="5" t="n"/>
+      <c r="D244" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -4488,7 +5460,11 @@
           <t>openaı</t>
         </is>
       </c>
-      <c r="D245" s="5" t="n"/>
+      <c r="D245" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -4504,7 +5480,11 @@
           <t>lit"e</t>
         </is>
       </c>
-      <c r="D246" s="5" t="n"/>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -4520,7 +5500,11 @@
           <t>netflix'e</t>
         </is>
       </c>
-      <c r="D247" s="5" t="n"/>
+      <c r="D247" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -4536,7 +5520,11 @@
           <t>üstünde</t>
         </is>
       </c>
-      <c r="D248" s="5" t="n"/>
+      <c r="D248" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -4552,7 +5540,11 @@
           <t>donuyor</t>
         </is>
       </c>
-      <c r="D249" s="5" t="n"/>
+      <c r="D249" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -4568,7 +5560,11 @@
           <t>ad</t>
         </is>
       </c>
-      <c r="D250" s="5" t="n"/>
+      <c r="D250" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -4584,7 +5580,11 @@
           <t>car</t>
         </is>
       </c>
-      <c r="D251" s="5" t="n"/>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -4600,7 +5600,11 @@
           <t>full</t>
         </is>
       </c>
-      <c r="D252" s="5" t="n"/>
+      <c r="D252" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -4616,7 +5620,11 @@
           <t>kelimeyi</t>
         </is>
       </c>
-      <c r="D253" s="5" t="n"/>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -4632,7 +5640,11 @@
           <t>burnout</t>
         </is>
       </c>
-      <c r="D254" s="5" t="n"/>
+      <c r="D254" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -4648,7 +5660,11 @@
           <t>chatgpt'ye</t>
         </is>
       </c>
-      <c r="D255" s="5" t="n"/>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -4664,7 +5680,11 @@
           <t>meme'yi</t>
         </is>
       </c>
-      <c r="D256" s="5" t="n"/>
+      <c r="D256" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -4680,7 +5700,11 @@
           <t>staff</t>
         </is>
       </c>
-      <c r="D257" s="5" t="n"/>
+      <c r="D257" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -4696,7 +5720,11 @@
           <t>indie</t>
         </is>
       </c>
-      <c r="D258" s="5" t="n"/>
+      <c r="D258" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -4712,7 +5740,11 @@
           <t>model</t>
         </is>
       </c>
-      <c r="D259" s="5" t="n"/>
+      <c r="D259" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -4728,7 +5760,11 @@
           <t>dar</t>
         </is>
       </c>
-      <c r="D260" s="5" t="n"/>
+      <c r="D260" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -4744,7 +5780,11 @@
           <t>barbie</t>
         </is>
       </c>
-      <c r="D261" s="5" t="n"/>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -4760,7 +5800,11 @@
           <t>spor</t>
         </is>
       </c>
-      <c r="D262" s="5" t="n"/>
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -4776,7 +5820,11 @@
           <t>ve</t>
         </is>
       </c>
-      <c r="D263" s="5" t="n"/>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -4792,7 +5840,11 @@
           <t>wouldn't</t>
         </is>
       </c>
-      <c r="D264" s="5" t="n"/>
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -4808,7 +5860,11 @@
           <t>starbucks'a</t>
         </is>
       </c>
-      <c r="D265" s="5" t="n"/>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -4824,7 +5880,11 @@
           <t>playlist'i</t>
         </is>
       </c>
-      <c r="D266" s="5" t="n"/>
+      <c r="D266" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -4840,7 +5900,11 @@
           <t>model</t>
         </is>
       </c>
-      <c r="D267" s="5" t="n"/>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -4856,7 +5920,11 @@
           <t>gordon</t>
         </is>
       </c>
-      <c r="D268" s="5" t="n"/>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -4872,7 +5940,11 @@
           <t>that</t>
         </is>
       </c>
-      <c r="D269" s="5" t="n"/>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -4888,7 +5960,11 @@
           <t>open</t>
         </is>
       </c>
-      <c r="D270" s="5" t="n"/>
+      <c r="D270" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -4904,7 +5980,11 @@
           <t>sözlerini</t>
         </is>
       </c>
-      <c r="D271" s="5" t="n"/>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -4920,7 +6000,11 @@
           <t>yere</t>
         </is>
       </c>
-      <c r="D272" s="5" t="n"/>
+      <c r="D272" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -4936,7 +6020,11 @@
           <t>ormanı'na</t>
         </is>
       </c>
-      <c r="D273" s="5" t="n"/>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -4952,7 +6040,11 @@
           <t>func</t>
         </is>
       </c>
-      <c r="D274" s="5" t="n"/>
+      <c r="D274" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -4968,7 +6060,11 @@
           <t>hello</t>
         </is>
       </c>
-      <c r="D275" s="5" t="n"/>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -4984,7 +6080,11 @@
           <t>protein</t>
         </is>
       </c>
-      <c r="D276" s="5" t="n"/>
+      <c r="D276" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -5000,7 +6100,11 @@
           <t>electron</t>
         </is>
       </c>
-      <c r="D277" s="5" t="n"/>
+      <c r="D277" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -5016,7 +6120,11 @@
           <t>parent</t>
         </is>
       </c>
-      <c r="D278" s="5" t="n"/>
+      <c r="D278" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -5032,7 +6140,11 @@
           <t>value</t>
         </is>
       </c>
-      <c r="D279" s="5" t="n"/>
+      <c r="D279" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -5048,7 +6160,11 @@
           <t>code'ları</t>
         </is>
       </c>
-      <c r="D280" s="5" t="n"/>
+      <c r="D280" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -5064,7 +6180,11 @@
           <t>colombia</t>
         </is>
       </c>
-      <c r="D281" s="5" t="n"/>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -5080,7 +6200,11 @@
           <t>retro</t>
         </is>
       </c>
-      <c r="D282" s="5" t="n"/>
+      <c r="D282" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -5096,7 +6220,11 @@
           <t>business</t>
         </is>
       </c>
-      <c r="D283" s="5" t="n"/>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -5112,7 +6240,11 @@
           <t>bütün</t>
         </is>
       </c>
-      <c r="D284" s="5" t="n"/>
+      <c r="D284" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -5128,7 +6260,11 @@
           <t>sami</t>
         </is>
       </c>
-      <c r="D285" s="5" t="n"/>
+      <c r="D285" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -5144,7 +6280,11 @@
           <t>post'umu</t>
         </is>
       </c>
-      <c r="D286" s="5" t="n"/>
+      <c r="D286" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -5160,7 +6300,11 @@
           <t>dun</t>
         </is>
       </c>
-      <c r="D287" s="5" t="n"/>
+      <c r="D287" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -5176,7 +6320,11 @@
           <t>call'a</t>
         </is>
       </c>
-      <c r="D288" s="5" t="n"/>
+      <c r="D288" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -5192,7 +6340,11 @@
           <t>turntablea</t>
         </is>
       </c>
-      <c r="D289" s="5" t="n"/>
+      <c r="D289" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -5208,7 +6360,11 @@
           <t>"sorry,</t>
         </is>
       </c>
-      <c r="D290" s="5" t="n"/>
+      <c r="D290" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -5224,7 +6380,11 @@
           <t>things</t>
         </is>
       </c>
-      <c r="D291" s="5" t="n"/>
+      <c r="D291" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -5240,7 +6400,11 @@
           <t>banlanıyordu</t>
         </is>
       </c>
-      <c r="D292" s="5" t="n"/>
+      <c r="D292" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -5256,7 +6420,11 @@
           <t>protein</t>
         </is>
       </c>
-      <c r="D293" s="5" t="n"/>
+      <c r="D293" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -5272,7 +6440,11 @@
           <t>togg'un</t>
         </is>
       </c>
-      <c r="D294" s="5" t="n"/>
+      <c r="D294" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -5288,7 +6460,11 @@
           <t>just</t>
         </is>
       </c>
-      <c r="D295" s="5" t="n"/>
+      <c r="D295" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -5304,7 +6480,11 @@
           <t>churn</t>
         </is>
       </c>
-      <c r="D296" s="5" t="n"/>
+      <c r="D296" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -5320,7 +6500,11 @@
           <t>cümlesinden</t>
         </is>
       </c>
-      <c r="D297" s="5" t="n"/>
+      <c r="D297" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -5336,7 +6520,11 @@
           <t>patreon'da</t>
         </is>
       </c>
-      <c r="D298" s="5" t="n"/>
+      <c r="D298" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -5352,7 +6540,11 @@
           <t>itadakimasu</t>
         </is>
       </c>
-      <c r="D299" s="5" t="n"/>
+      <c r="D299" s="5" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -5368,7 +6560,11 @@
           <t>master</t>
         </is>
       </c>
-      <c r="D300" s="5" t="n"/>
+      <c r="D300" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -5384,7 +6580,11 @@
           <t>news</t>
         </is>
       </c>
-      <c r="D301" s="5" t="n"/>
+      <c r="D301" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -5400,7 +6600,11 @@
           <t>decoderımı</t>
         </is>
       </c>
-      <c r="D302" s="5" t="n"/>
+      <c r="D302" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -5416,7 +6620,11 @@
           <t>stars'ta</t>
         </is>
       </c>
-      <c r="D303" s="5" t="n"/>
+      <c r="D303" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -5432,7 +6640,11 @@
           <t>yazdi</t>
         </is>
       </c>
-      <c r="D304" s="5" t="n"/>
+      <c r="D304" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -5448,7 +6660,11 @@
           <t>model</t>
         </is>
       </c>
-      <c r="D305" s="5" t="n"/>
+      <c r="D305" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -5464,7 +6680,11 @@
           <t>supersetidir</t>
         </is>
       </c>
-      <c r="D306" s="5" t="n"/>
+      <c r="D306" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -5480,7 +6700,11 @@
           <t>netflix</t>
         </is>
       </c>
-      <c r="D307" s="5" t="n"/>
+      <c r="D307" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -5496,7 +6720,11 @@
           <t>gym'deki</t>
         </is>
       </c>
-      <c r="D308" s="5" t="n"/>
+      <c r="D308" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -5512,7 +6740,11 @@
           <t>ink'i</t>
         </is>
       </c>
-      <c r="D309" s="5" t="n"/>
+      <c r="D309" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -5528,7 +6760,11 @@
           <t>ip'sini</t>
         </is>
       </c>
-      <c r="D310" s="5" t="n"/>
+      <c r="D310" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -5544,7 +6780,11 @@
           <t>online</t>
         </is>
       </c>
-      <c r="D311" s="5" t="n"/>
+      <c r="D311" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -5560,7 +6800,11 @@
           <t>de</t>
         </is>
       </c>
-      <c r="D312" s="5" t="n"/>
+      <c r="D312" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -5576,7 +6820,11 @@
           <t>elbise</t>
         </is>
       </c>
-      <c r="D313" s="5" t="n"/>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -5592,7 +6840,11 @@
           <t>playlist'i</t>
         </is>
       </c>
-      <c r="D314" s="5" t="n"/>
+      <c r="D314" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -5608,7 +6860,11 @@
           <t>regional</t>
         </is>
       </c>
-      <c r="D315" s="5" t="n"/>
+      <c r="D315" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -5624,7 +6880,11 @@
           <t>kimse</t>
         </is>
       </c>
-      <c r="D316" s="5" t="n"/>
+      <c r="D316" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -5640,7 +6900,11 @@
           <t>navigasyon</t>
         </is>
       </c>
-      <c r="D317" s="5" t="n"/>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -5656,7 +6920,11 @@
           <t>bi</t>
         </is>
       </c>
-      <c r="D318" s="5" t="n"/>
+      <c r="D318" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -5672,7 +6940,11 @@
           <t>olmuş</t>
         </is>
       </c>
-      <c r="D319" s="5" t="n"/>
+      <c r="D319" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -5688,7 +6960,11 @@
           <t>title'ı</t>
         </is>
       </c>
-      <c r="D320" s="5" t="n"/>
+      <c r="D320" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -5704,7 +6980,11 @@
           <t>web</t>
         </is>
       </c>
-      <c r="D321" s="5" t="n"/>
+      <c r="D321" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -5720,7 +7000,11 @@
           <t>son</t>
         </is>
       </c>
-      <c r="D322" s="5" t="n"/>
+      <c r="D322" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -5736,7 +7020,11 @@
           <t>satir</t>
         </is>
       </c>
-      <c r="D323" s="5" t="n"/>
+      <c r="D323" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -5752,7 +7040,11 @@
           <t>housewarming</t>
         </is>
       </c>
-      <c r="D324" s="5" t="n"/>
+      <c r="D324" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -5768,7 +7060,11 @@
           <t>pierre</t>
         </is>
       </c>
-      <c r="D325" s="5" t="n"/>
+      <c r="D325" s="5" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -5784,7 +7080,11 @@
           <t>djlik</t>
         </is>
       </c>
-      <c r="D326" s="5" t="n"/>
+      <c r="D326" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -5800,7 +7100,11 @@
           <t>speech'i</t>
         </is>
       </c>
-      <c r="D327" s="5" t="n"/>
+      <c r="D327" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -5816,7 +7120,11 @@
           <t>cocukken</t>
         </is>
       </c>
-      <c r="D328" s="5" t="n"/>
+      <c r="D328" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -5832,7 +7140,11 @@
           <t>oluyorsunuz</t>
         </is>
       </c>
-      <c r="D329" s="5" t="n"/>
+      <c r="D329" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -5848,7 +7160,11 @@
           <t>motor</t>
         </is>
       </c>
-      <c r="D330" s="5" t="n"/>
+      <c r="D330" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -5864,7 +7180,11 @@
           <t>it</t>
         </is>
       </c>
-      <c r="D331" s="5" t="n"/>
+      <c r="D331" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -5880,7 +7200,11 @@
           <t>ne</t>
         </is>
       </c>
-      <c r="D332" s="5" t="n"/>
+      <c r="D332" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -5896,7 +7220,11 @@
           <t>bowl'cu</t>
         </is>
       </c>
-      <c r="D333" s="5" t="n"/>
+      <c r="D333" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -5912,7 +7240,11 @@
           <t>stories'i</t>
         </is>
       </c>
-      <c r="D334" s="5" t="n"/>
+      <c r="D334" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -5928,7 +7260,11 @@
           <t>intern</t>
         </is>
       </c>
-      <c r="D335" s="5" t="n"/>
+      <c r="D335" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -5944,7 +7280,11 @@
           <t>gelen</t>
         </is>
       </c>
-      <c r="D336" s="5" t="n"/>
+      <c r="D336" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -5960,7 +7300,11 @@
           <t>ticket'lari</t>
         </is>
       </c>
-      <c r="D337" s="5" t="n"/>
+      <c r="D337" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -5976,7 +7320,11 @@
           <t>post'larını</t>
         </is>
       </c>
-      <c r="D338" s="5" t="n"/>
+      <c r="D338" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -5992,7 +7340,11 @@
           <t>soruyor,</t>
         </is>
       </c>
-      <c r="D339" s="5" t="n"/>
+      <c r="D339" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -6008,7 +7360,11 @@
           <t>izlerken</t>
         </is>
       </c>
-      <c r="D340" s="5" t="n"/>
+      <c r="D340" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -6024,7 +7380,11 @@
           <t>iyi</t>
         </is>
       </c>
-      <c r="D341" s="5" t="n"/>
+      <c r="D341" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -6040,7 +7400,11 @@
           <t>ingilizce</t>
         </is>
       </c>
-      <c r="D342" s="5" t="n"/>
+      <c r="D342" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -6056,7 +7420,11 @@
           <t>kaldım</t>
         </is>
       </c>
-      <c r="D343" s="5" t="n"/>
+      <c r="D343" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -6072,7 +7440,11 @@
           <t>ticks</t>
         </is>
       </c>
-      <c r="D344" s="5" t="n"/>
+      <c r="D344" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -6088,7 +7460,11 @@
           <t>ibrahimoviç'le</t>
         </is>
       </c>
-      <c r="D345" s="5" t="n"/>
+      <c r="D345" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -6104,7 +7480,11 @@
           <t>öğrenme</t>
         </is>
       </c>
-      <c r="D346" s="5" t="n"/>
+      <c r="D346" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -6120,7 +7500,11 @@
           <t>coursera'daki</t>
         </is>
       </c>
-      <c r="D347" s="5" t="n"/>
+      <c r="D347" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -6136,7 +7520,11 @@
           <t>zümrenin</t>
         </is>
       </c>
-      <c r="D348" s="5" t="n"/>
+      <c r="D348" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -6152,7 +7540,11 @@
           <t>crypto</t>
         </is>
       </c>
-      <c r="D349" s="5" t="n"/>
+      <c r="D349" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -6168,7 +7560,11 @@
           <t>super</t>
         </is>
       </c>
-      <c r="D350" s="5" t="n"/>
+      <c r="D350" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -6184,7 +7580,11 @@
           <t>nişan</t>
         </is>
       </c>
-      <c r="D351" s="5" t="n"/>
+      <c r="D351" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -6200,7 +7600,11 @@
           <t>tote</t>
         </is>
       </c>
-      <c r="D352" s="5" t="n"/>
+      <c r="D352" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -6216,7 +7620,11 @@
           <t>assistant'ı</t>
         </is>
       </c>
-      <c r="D353" s="5" t="n"/>
+      <c r="D353" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -6232,7 +7640,11 @@
           <t>ingilizce</t>
         </is>
       </c>
-      <c r="D354" s="5" t="n"/>
+      <c r="D354" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -6248,7 +7660,11 @@
           <t>platform</t>
         </is>
       </c>
-      <c r="D355" s="5" t="n"/>
+      <c r="D355" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -6264,7 +7680,11 @@
           <t>denedim,</t>
         </is>
       </c>
-      <c r="D356" s="5" t="n"/>
+      <c r="D356" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -6280,7 +7700,11 @@
           <t>amino</t>
         </is>
       </c>
-      <c r="D357" s="5" t="n"/>
+      <c r="D357" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -6296,7 +7720,11 @@
           <t>are</t>
         </is>
       </c>
-      <c r="D358" s="5" t="n"/>
+      <c r="D358" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -6312,7 +7740,11 @@
           <t>native</t>
         </is>
       </c>
-      <c r="D359" s="5" t="n"/>
+      <c r="D359" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -6328,7 +7760,11 @@
           <t>apply'la</t>
         </is>
       </c>
-      <c r="D360" s="5" t="n"/>
+      <c r="D360" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -6344,7 +7780,11 @@
           <t>manager"</t>
         </is>
       </c>
-      <c r="D361" s="5" t="n"/>
+      <c r="D361" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -6360,7 +7800,11 @@
           <t>fitness</t>
         </is>
       </c>
-      <c r="D362" s="5" t="n"/>
+      <c r="D362" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -6376,7 +7820,11 @@
           <t>spor</t>
         </is>
       </c>
-      <c r="D363" s="5" t="n"/>
+      <c r="D363" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -6392,7 +7840,11 @@
           <t>kalsiyum</t>
         </is>
       </c>
-      <c r="D364" s="5" t="n"/>
+      <c r="D364" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -6408,7 +7860,11 @@
           <t>kadıköy'de</t>
         </is>
       </c>
-      <c r="D365" s="5" t="n"/>
+      <c r="D365" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -6424,7 +7880,11 @@
           <t>turunda</t>
         </is>
       </c>
-      <c r="D366" s="5" t="n"/>
+      <c r="D366" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -6440,7 +7900,11 @@
           <t>"x</t>
         </is>
       </c>
-      <c r="D367" s="5" t="n"/>
+      <c r="D367" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -6456,7 +7920,11 @@
           <t>partner'im</t>
         </is>
       </c>
-      <c r="D368" s="5" t="n"/>
+      <c r="D368" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -6472,7 +7940,11 @@
           <t>executive</t>
         </is>
       </c>
-      <c r="D369" s="5" t="n"/>
+      <c r="D369" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -6488,7 +7960,11 @@
           <t>spyware</t>
         </is>
       </c>
-      <c r="D370" s="5" t="n"/>
+      <c r="D370" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -6504,7 +7980,11 @@
           <t>her</t>
         </is>
       </c>
-      <c r="D371" s="5" t="n"/>
+      <c r="D371" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -6520,7 +8000,11 @@
           <t>linke</t>
         </is>
       </c>
-      <c r="D372" s="5" t="n"/>
+      <c r="D372" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -6536,7 +8020,11 @@
           <t>insanlık</t>
         </is>
       </c>
-      <c r="D373" s="5" t="n"/>
+      <c r="D373" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -6552,7 +8040,11 @@
           <t>göre</t>
         </is>
       </c>
-      <c r="D374" s="5" t="n"/>
+      <c r="D374" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -6568,7 +8060,11 @@
           <t>but</t>
         </is>
       </c>
-      <c r="D375" s="5" t="n"/>
+      <c r="D375" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -6584,7 +8080,11 @@
           <t>later</t>
         </is>
       </c>
-      <c r="D376" s="5" t="n"/>
+      <c r="D376" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -6600,7 +8100,11 @@
           <t>freelancer</t>
         </is>
       </c>
-      <c r="D377" s="5" t="n"/>
+      <c r="D377" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -6616,7 +8120,11 @@
           <t>planner'ımız</t>
         </is>
       </c>
-      <c r="D378" s="5" t="n"/>
+      <c r="D378" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -6632,7 +8140,11 @@
           <t>ingilizce</t>
         </is>
       </c>
-      <c r="D379" s="5" t="n"/>
+      <c r="D379" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -6648,7 +8160,11 @@
           <t>code'u</t>
         </is>
       </c>
-      <c r="D380" s="5" t="n"/>
+      <c r="D380" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -6664,7 +8180,11 @@
           <t>we</t>
         </is>
       </c>
-      <c r="D381" s="5" t="n"/>
+      <c r="D381" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -6680,7 +8200,11 @@
           <t>schedule'ını</t>
         </is>
       </c>
-      <c r="D382" s="5" t="n"/>
+      <c r="D382" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -6696,7 +8220,11 @@
           <t>alarmdan</t>
         </is>
       </c>
-      <c r="D383" s="5" t="n"/>
+      <c r="D383" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -6712,7 +8240,11 @@
           <t>server</t>
         </is>
       </c>
-      <c r="D384" s="5" t="n"/>
+      <c r="D384" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -6728,7 +8260,11 @@
           <t>us</t>
         </is>
       </c>
-      <c r="D385" s="5" t="n"/>
+      <c r="D385" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -6744,7 +8280,11 @@
           <t>obsidian'a</t>
         </is>
       </c>
-      <c r="D386" s="5" t="n"/>
+      <c r="D386" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -6760,7 +8300,11 @@
           <t>deck'imle</t>
         </is>
       </c>
-      <c r="D387" s="5" t="n"/>
+      <c r="D387" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -6776,7 +8320,11 @@
           <t>subreddit</t>
         </is>
       </c>
-      <c r="D388" s="5" t="n"/>
+      <c r="D388" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -6792,7 +8340,11 @@
           <t>yeni</t>
         </is>
       </c>
-      <c r="D389" s="5" t="n"/>
+      <c r="D389" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -6808,7 +8360,11 @@
           <t>boğaziçi'nin</t>
         </is>
       </c>
-      <c r="D390" s="5" t="n"/>
+      <c r="D390" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -6824,7 +8380,11 @@
           <t>tracker'ımı</t>
         </is>
       </c>
-      <c r="D391" s="5" t="n"/>
+      <c r="D391" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -6840,7 +8400,11 @@
           <t>love</t>
         </is>
       </c>
-      <c r="D392" s="5" t="n"/>
+      <c r="D392" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -6856,7 +8420,11 @@
           <t>odunlarla</t>
         </is>
       </c>
-      <c r="D393" s="5" t="n"/>
+      <c r="D393" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -6872,7 +8440,11 @@
           <t>kadar</t>
         </is>
       </c>
-      <c r="D394" s="5" t="n"/>
+      <c r="D394" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -6888,7 +8460,11 @@
           <t>crush'im</t>
         </is>
       </c>
-      <c r="D395" s="5" t="n"/>
+      <c r="D395" s="5" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -6904,7 +8480,11 @@
           <t>teleferikte</t>
         </is>
       </c>
-      <c r="D396" s="5" t="n"/>
+      <c r="D396" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -6920,7 +8500,11 @@
           <t>kasdjkajh</t>
         </is>
       </c>
-      <c r="D397" s="5" t="n"/>
+      <c r="D397" s="5" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -6936,7 +8520,11 @@
           <t>uygulama</t>
         </is>
       </c>
-      <c r="D398" s="5" t="n"/>
+      <c r="D398" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -6952,7 +8540,11 @@
           <t>of</t>
         </is>
       </c>
-      <c r="D399" s="5" t="n"/>
+      <c r="D399" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -6968,7 +8560,11 @@
           <t>güney</t>
         </is>
       </c>
-      <c r="D400" s="5" t="n"/>
+      <c r="D400" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -6984,7 +8580,11 @@
           <t>stream</t>
         </is>
       </c>
-      <c r="D401" s="5" t="n"/>
+      <c r="D401" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -7000,7 +8600,11 @@
           <t>believe</t>
         </is>
       </c>
-      <c r="D402" s="5" t="n"/>
+      <c r="D402" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -7016,7 +8620,11 @@
           <t>house</t>
         </is>
       </c>
-      <c r="D403" s="5" t="n"/>
+      <c r="D403" s="5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
